--- a/VerveStacks_ARE_grids_kan/vt_vervestacks_ARE_v1.xlsx
+++ b/VerveStacks_ARE_grids_kan/vt_vervestacks_ARE_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{779FDCE9-6014-43E2-B252-72F0DB0B929F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29A0C185-B261-4B45-A9F8-9E8D961B3A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B8703782-8BC1-43EA-91B9-6D3E80F8811D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CC49AEDB-DEEA-48B4-8487-5425ADBB12A0}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2407,7 +2407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC96FAA2-5F25-4390-B811-94FDA00213D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53C7464-69EB-4D21-B03B-96C5A022AE94}">
   <dimension ref="B9:V139"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2495,19 +2495,19 @@
         <v>21</v>
       </c>
       <c r="F11">
-        <v>0.30867165000000002</v>
+        <v>0.19653039000000003</v>
       </c>
       <c r="G11">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="H11">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="I11">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="J11">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="K11" t="s">
         <v>19</v>
@@ -2557,19 +2557,19 @@
         <v>21</v>
       </c>
       <c r="F12">
-        <v>0.31576755000000001</v>
+        <v>0.20104833000000003</v>
       </c>
       <c r="G12">
-        <v>1967</v>
+        <v>2445</v>
       </c>
       <c r="H12">
-        <v>25.2</v>
+        <v>30.4</v>
       </c>
       <c r="I12">
-        <v>2.73</v>
+        <v>3.52</v>
       </c>
       <c r="J12">
-        <v>0.76759999999999995</v>
+        <v>0.72770000000000001</v>
       </c>
       <c r="K12" t="s">
         <v>22</v>
@@ -2619,7 +2619,7 @@
         <v>21</v>
       </c>
       <c r="F13">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G13">
         <v>1365</v>
@@ -2681,7 +2681,7 @@
         <v>26</v>
       </c>
       <c r="F14">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G14">
         <v>1365</v>
@@ -2743,7 +2743,7 @@
         <v>28</v>
       </c>
       <c r="F15">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G15">
         <v>1365</v>
@@ -2805,7 +2805,7 @@
         <v>30</v>
       </c>
       <c r="F16">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G16">
         <v>1365</v>
@@ -2867,7 +2867,7 @@
         <v>32</v>
       </c>
       <c r="F17">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G17">
         <v>1365</v>
@@ -2929,7 +2929,7 @@
         <v>32</v>
       </c>
       <c r="F18">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G18">
         <v>1365</v>
@@ -2991,7 +2991,7 @@
         <v>32</v>
       </c>
       <c r="F19">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G19">
         <v>1365</v>
@@ -3053,7 +3053,7 @@
         <v>32</v>
       </c>
       <c r="F20">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G20">
         <v>1365</v>
@@ -3115,7 +3115,7 @@
         <v>32</v>
       </c>
       <c r="F21">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="G21">
         <v>1365</v>
@@ -3177,7 +3177,7 @@
         <v>38</v>
       </c>
       <c r="F22">
-        <v>0.42721875000000004</v>
+        <v>0.3310945312500001</v>
       </c>
       <c r="G22">
         <v>1365</v>
@@ -3239,7 +3239,7 @@
         <v>38</v>
       </c>
       <c r="F23">
-        <v>0.36618750000000005</v>
+        <v>0.28379531250000006</v>
       </c>
       <c r="G23">
         <v>1365</v>
@@ -3301,7 +3301,7 @@
         <v>38</v>
       </c>
       <c r="F24">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G24">
         <v>1365</v>
@@ -3363,7 +3363,7 @@
         <v>38</v>
       </c>
       <c r="F25">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G25">
         <v>1365</v>
@@ -3425,7 +3425,7 @@
         <v>38</v>
       </c>
       <c r="F26">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G26">
         <v>1365</v>
@@ -3487,7 +3487,7 @@
         <v>38</v>
       </c>
       <c r="F27">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G27">
         <v>1365</v>
@@ -3549,7 +3549,7 @@
         <v>38</v>
       </c>
       <c r="F28">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G28">
         <v>1365</v>
@@ -3611,7 +3611,7 @@
         <v>38</v>
       </c>
       <c r="F29">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G29">
         <v>1365</v>
@@ -3673,7 +3673,7 @@
         <v>38</v>
       </c>
       <c r="F30">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G30">
         <v>1365</v>
@@ -3735,7 +3735,7 @@
         <v>48</v>
       </c>
       <c r="F31">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="G31">
         <v>1365</v>
@@ -3797,7 +3797,7 @@
         <v>50</v>
       </c>
       <c r="F32">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G32">
         <v>1365</v>
@@ -3859,7 +3859,7 @@
         <v>52</v>
       </c>
       <c r="F33">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="G33">
         <v>1365</v>
@@ -3921,7 +3921,7 @@
         <v>52</v>
       </c>
       <c r="F34">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="G34">
         <v>1365</v>
@@ -3983,7 +3983,7 @@
         <v>52</v>
       </c>
       <c r="F35">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="G35">
         <v>1365</v>
@@ -4045,7 +4045,7 @@
         <v>56</v>
       </c>
       <c r="F36">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G36">
         <v>1365</v>
@@ -4107,7 +4107,7 @@
         <v>56</v>
       </c>
       <c r="F37">
-        <v>0.47197499999999998</v>
+        <v>0.36578062499999997</v>
       </c>
       <c r="G37">
         <v>1365</v>
@@ -4169,7 +4169,7 @@
         <v>56</v>
       </c>
       <c r="F38">
-        <v>0.47197499999999998</v>
+        <v>0.36578062499999997</v>
       </c>
       <c r="G38">
         <v>1365</v>
@@ -4231,7 +4231,7 @@
         <v>56</v>
       </c>
       <c r="F39">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G39">
         <v>1365</v>
@@ -4293,7 +4293,7 @@
         <v>56</v>
       </c>
       <c r="F40">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G40">
         <v>1365</v>
@@ -4355,7 +4355,7 @@
         <v>62</v>
       </c>
       <c r="F41">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G41">
         <v>1365</v>
@@ -4417,7 +4417,7 @@
         <v>62</v>
       </c>
       <c r="F42">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G42">
         <v>1365</v>
@@ -4479,7 +4479,7 @@
         <v>62</v>
       </c>
       <c r="F43">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G43">
         <v>1365</v>
@@ -4541,7 +4541,7 @@
         <v>62</v>
       </c>
       <c r="F44">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G44">
         <v>1365</v>
@@ -4603,7 +4603,7 @@
         <v>67</v>
       </c>
       <c r="F45">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="G45">
         <v>1365</v>
@@ -4665,7 +4665,7 @@
         <v>67</v>
       </c>
       <c r="F46">
-        <v>0.32550000000000007</v>
+        <v>0.25226250000000006</v>
       </c>
       <c r="G46">
         <v>1365</v>
@@ -4727,7 +4727,7 @@
         <v>26</v>
       </c>
       <c r="F47">
-        <v>0.47197499999999998</v>
+        <v>0.36578062500000003</v>
       </c>
       <c r="G47">
         <v>1365</v>
@@ -4789,7 +4789,7 @@
         <v>26</v>
       </c>
       <c r="F48">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G48">
         <v>1365</v>
@@ -4851,7 +4851,7 @@
         <v>26</v>
       </c>
       <c r="F49">
-        <v>0.44349375000000002</v>
+        <v>0.34370765625000005</v>
       </c>
       <c r="G49">
         <v>1365</v>
@@ -4913,7 +4913,7 @@
         <v>48</v>
       </c>
       <c r="F50">
-        <v>0.48825000000000002</v>
+        <v>0.37839375000000003</v>
       </c>
       <c r="G50">
         <v>1365</v>
@@ -4975,7 +4975,7 @@
         <v>74</v>
       </c>
       <c r="F51">
-        <v>0.44349375000000002</v>
+        <v>0.3437076562500001</v>
       </c>
       <c r="G51">
         <v>1365</v>
@@ -5037,7 +5037,7 @@
         <v>52</v>
       </c>
       <c r="F52">
-        <v>0.18716250000000001</v>
+        <v>0.14505093750000003</v>
       </c>
       <c r="G52">
         <v>1365</v>
@@ -5099,7 +5099,7 @@
         <v>52</v>
       </c>
       <c r="F53">
-        <v>0.18716250000000001</v>
+        <v>0.14505093750000003</v>
       </c>
       <c r="G53">
         <v>1365</v>
@@ -5161,7 +5161,7 @@
         <v>18</v>
       </c>
       <c r="F54">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G54">
         <v>1365</v>
@@ -5223,7 +5223,7 @@
         <v>18</v>
       </c>
       <c r="F55">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G55">
         <v>1365</v>
@@ -5285,7 +5285,7 @@
         <v>18</v>
       </c>
       <c r="F56">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G56">
         <v>1365</v>
@@ -5347,7 +5347,7 @@
         <v>18</v>
       </c>
       <c r="F57">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G57">
         <v>1365</v>
@@ -5409,7 +5409,7 @@
         <v>18</v>
       </c>
       <c r="F58">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G58">
         <v>1365</v>
@@ -5471,7 +5471,7 @@
         <v>18</v>
       </c>
       <c r="F59">
-        <v>0.21564375000000005</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G59">
         <v>1365</v>
@@ -5533,7 +5533,7 @@
         <v>18</v>
       </c>
       <c r="F60">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G60">
         <v>1365</v>
@@ -5595,7 +5595,7 @@
         <v>18</v>
       </c>
       <c r="F61">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G61">
         <v>1365</v>
@@ -5657,7 +5657,7 @@
         <v>18</v>
       </c>
       <c r="F62">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G62">
         <v>1365</v>
@@ -5719,7 +5719,7 @@
         <v>18</v>
       </c>
       <c r="F63">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G63">
         <v>1365</v>
@@ -5781,7 +5781,7 @@
         <v>18</v>
       </c>
       <c r="F64">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G64">
         <v>1365</v>
@@ -5843,7 +5843,7 @@
         <v>18</v>
       </c>
       <c r="F65">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G65">
         <v>1365</v>
@@ -5905,7 +5905,7 @@
         <v>18</v>
       </c>
       <c r="F66">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G66">
         <v>1365</v>
@@ -5967,7 +5967,7 @@
         <v>18</v>
       </c>
       <c r="F67">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="G67">
         <v>1365</v>
@@ -6029,7 +6029,7 @@
         <v>18</v>
       </c>
       <c r="F68">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="G68">
         <v>1365</v>
@@ -6091,7 +6091,7 @@
         <v>18</v>
       </c>
       <c r="F69">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="G69">
         <v>1365</v>
@@ -6153,7 +6153,7 @@
         <v>52</v>
       </c>
       <c r="F70">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G70">
         <v>1365</v>
@@ -6215,7 +6215,7 @@
         <v>52</v>
       </c>
       <c r="F71">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G71">
         <v>1365</v>
@@ -6277,7 +6277,7 @@
         <v>38</v>
       </c>
       <c r="F72">
-        <v>0.22378125000000004</v>
+        <v>0.17343046875000001</v>
       </c>
       <c r="G72">
         <v>1365</v>
@@ -6339,7 +6339,7 @@
         <v>38</v>
       </c>
       <c r="F73">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="G73">
         <v>1365</v>
@@ -6401,7 +6401,7 @@
         <v>38</v>
       </c>
       <c r="F74">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000004</v>
       </c>
       <c r="G74">
         <v>1365</v>
@@ -6463,7 +6463,7 @@
         <v>48</v>
       </c>
       <c r="F75">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G75">
         <v>1365</v>
@@ -6525,7 +6525,7 @@
         <v>48</v>
       </c>
       <c r="F76">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G76">
         <v>1365</v>
@@ -6587,7 +6587,7 @@
         <v>50</v>
       </c>
       <c r="F77">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G77">
         <v>1365</v>
@@ -6649,7 +6649,7 @@
         <v>50</v>
       </c>
       <c r="F78">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G78">
         <v>1365</v>
@@ -6711,7 +6711,7 @@
         <v>50</v>
       </c>
       <c r="F79">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G79">
         <v>1365</v>
@@ -6773,7 +6773,7 @@
         <v>50</v>
       </c>
       <c r="F80">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G80">
         <v>1365</v>
@@ -6835,7 +6835,7 @@
         <v>105</v>
       </c>
       <c r="F81">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G81">
         <v>1365</v>
@@ -6897,7 +6897,7 @@
         <v>105</v>
       </c>
       <c r="F82">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G82">
         <v>1365</v>
@@ -6959,7 +6959,7 @@
         <v>108</v>
       </c>
       <c r="F83">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G83">
         <v>1365</v>
@@ -7021,7 +7021,7 @@
         <v>108</v>
       </c>
       <c r="F84">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G84">
         <v>1365</v>
@@ -7083,7 +7083,7 @@
         <v>108</v>
       </c>
       <c r="F85">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G85">
         <v>1365</v>
@@ -7145,7 +7145,7 @@
         <v>108</v>
       </c>
       <c r="F86">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G86">
         <v>1365</v>
@@ -7207,7 +7207,7 @@
         <v>108</v>
       </c>
       <c r="F87">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G87">
         <v>1365</v>
@@ -7269,7 +7269,7 @@
         <v>108</v>
       </c>
       <c r="F88">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G88">
         <v>1365</v>
@@ -7331,7 +7331,7 @@
         <v>108</v>
       </c>
       <c r="F89">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G89">
         <v>1365</v>
@@ -7393,7 +7393,7 @@
         <v>108</v>
       </c>
       <c r="F90">
-        <v>0.22785</v>
+        <v>0.17658375000000004</v>
       </c>
       <c r="G90">
         <v>1365</v>
@@ -7455,7 +7455,7 @@
         <v>108</v>
       </c>
       <c r="F91">
-        <v>0.22785</v>
+        <v>0.17658375000000004</v>
       </c>
       <c r="G91">
         <v>1365</v>
@@ -7517,7 +7517,7 @@
         <v>105</v>
       </c>
       <c r="F92">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G92">
         <v>1365</v>
@@ -7579,7 +7579,7 @@
         <v>105</v>
       </c>
       <c r="F93">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G93">
         <v>1365</v>
@@ -7641,7 +7641,7 @@
         <v>105</v>
       </c>
       <c r="F94">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G94">
         <v>1365</v>
@@ -7703,7 +7703,7 @@
         <v>105</v>
       </c>
       <c r="F95">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G95">
         <v>1365</v>
@@ -7765,7 +7765,7 @@
         <v>105</v>
       </c>
       <c r="F96">
-        <v>0.2522625</v>
+        <v>0.19550343749999999</v>
       </c>
       <c r="G96">
         <v>1365</v>
@@ -7827,7 +7827,7 @@
         <v>26</v>
       </c>
       <c r="F97">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G97">
         <v>1365</v>
@@ -7889,7 +7889,7 @@
         <v>26</v>
       </c>
       <c r="F98">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G98">
         <v>1365</v>
@@ -7951,7 +7951,7 @@
         <v>105</v>
       </c>
       <c r="F99">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G99">
         <v>1365</v>
@@ -8013,7 +8013,7 @@
         <v>105</v>
       </c>
       <c r="F100">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G100">
         <v>1365</v>
@@ -8075,7 +8075,7 @@
         <v>127</v>
       </c>
       <c r="F101">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G101">
         <v>1365</v>
@@ -8137,7 +8137,7 @@
         <v>127</v>
       </c>
       <c r="F102">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G102">
         <v>1365</v>
@@ -8199,7 +8199,7 @@
         <v>127</v>
       </c>
       <c r="F103">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G103">
         <v>1365</v>
@@ -8261,7 +8261,7 @@
         <v>108</v>
       </c>
       <c r="F104">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G104">
         <v>1365</v>
@@ -8323,7 +8323,7 @@
         <v>108</v>
       </c>
       <c r="F105">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G105">
         <v>1365</v>
@@ -8385,7 +8385,7 @@
         <v>108</v>
       </c>
       <c r="F106">
-        <v>0.21564375000000002</v>
+        <v>0.16712390625000001</v>
       </c>
       <c r="G106">
         <v>1365</v>
@@ -8447,7 +8447,7 @@
         <v>52</v>
       </c>
       <c r="F107">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G107">
         <v>1365</v>
@@ -8509,7 +8509,7 @@
         <v>52</v>
       </c>
       <c r="F108">
-        <v>0.23598749999999999</v>
+        <v>0.18289031250000001</v>
       </c>
       <c r="G108">
         <v>1365</v>
@@ -8571,7 +8571,7 @@
         <v>48</v>
       </c>
       <c r="F109">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="G109">
         <v>1365</v>
@@ -8633,7 +8633,7 @@
         <v>48</v>
       </c>
       <c r="F110">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="G110">
         <v>1365</v>
@@ -8695,7 +8695,7 @@
         <v>48</v>
       </c>
       <c r="F111">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="G111">
         <v>1365</v>
@@ -8757,7 +8757,7 @@
         <v>48</v>
       </c>
       <c r="F112">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="G112">
         <v>1365</v>
@@ -8819,7 +8819,7 @@
         <v>62</v>
       </c>
       <c r="F113">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="G113">
         <v>1365</v>
@@ -8881,7 +8881,7 @@
         <v>62</v>
       </c>
       <c r="F114">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="G114">
         <v>1365</v>
@@ -8943,7 +8943,7 @@
         <v>62</v>
       </c>
       <c r="F115">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="G115">
         <v>1365</v>
@@ -9005,7 +9005,7 @@
         <v>62</v>
       </c>
       <c r="F116">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="G116">
         <v>1365</v>
@@ -9067,7 +9067,7 @@
         <v>62</v>
       </c>
       <c r="F117">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="G117">
         <v>1365</v>
@@ -9129,7 +9129,7 @@
         <v>62</v>
       </c>
       <c r="F118">
-        <v>0.26853750000000004</v>
+        <v>0.20811656249999999</v>
       </c>
       <c r="G118">
         <v>1365</v>
@@ -9191,7 +9191,7 @@
         <v>105</v>
       </c>
       <c r="F119">
-        <v>0.28074374999999996</v>
+        <v>0.21757640624999997</v>
       </c>
       <c r="G119">
         <v>1365</v>
@@ -9253,7 +9253,7 @@
         <v>48</v>
       </c>
       <c r="F120">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="G120">
         <v>1365</v>
@@ -9315,7 +9315,7 @@
         <v>127</v>
       </c>
       <c r="F121">
-        <v>0.28074374999999996</v>
+        <v>0.21757640624999997</v>
       </c>
       <c r="G121">
         <v>1365</v>
@@ -9377,7 +9377,7 @@
         <v>21</v>
       </c>
       <c r="F122">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="G122">
         <v>1365</v>
@@ -9439,7 +9439,7 @@
         <v>21</v>
       </c>
       <c r="F123">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="G123">
         <v>1365</v>
@@ -9501,7 +9501,7 @@
         <v>21</v>
       </c>
       <c r="F124">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="G124">
         <v>1365</v>
@@ -9563,7 +9563,7 @@
         <v>21</v>
       </c>
       <c r="F125">
-        <v>0.29701875</v>
+        <v>0.23018953125000002</v>
       </c>
       <c r="G125">
         <v>1365</v>
@@ -9625,7 +9625,7 @@
         <v>153</v>
       </c>
       <c r="F126">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G126">
         <v>1365</v>
@@ -9687,7 +9687,7 @@
         <v>105</v>
       </c>
       <c r="F127">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G127">
         <v>1365</v>
@@ -9749,7 +9749,7 @@
         <v>48</v>
       </c>
       <c r="F128">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G128">
         <v>1365</v>
@@ -9811,7 +9811,7 @@
         <v>18</v>
       </c>
       <c r="F129">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G129">
         <v>1365</v>
@@ -9873,7 +9873,7 @@
         <v>38</v>
       </c>
       <c r="F130">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G130">
         <v>1365</v>
@@ -9935,7 +9935,7 @@
         <v>56</v>
       </c>
       <c r="F131">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G131">
         <v>1365</v>
@@ -9997,7 +9997,7 @@
         <v>32</v>
       </c>
       <c r="F132">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G132">
         <v>1365</v>
@@ -10059,7 +10059,7 @@
         <v>108</v>
       </c>
       <c r="F133">
-        <v>0.28982625000000006</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G133">
         <v>1365</v>
@@ -10121,7 +10121,7 @@
         <v>52</v>
       </c>
       <c r="F134">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G134">
         <v>1365</v>
@@ -10183,7 +10183,7 @@
         <v>50</v>
       </c>
       <c r="F135">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G135">
         <v>1365</v>
@@ -10245,7 +10245,7 @@
         <v>67</v>
       </c>
       <c r="F136">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G136">
         <v>1365</v>
@@ -10307,7 +10307,7 @@
         <v>127</v>
       </c>
       <c r="F137">
-        <v>0.28982625000000006</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G137">
         <v>1365</v>
@@ -10369,7 +10369,7 @@
         <v>74</v>
       </c>
       <c r="F138">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G138">
         <v>1365</v>
@@ -10431,7 +10431,7 @@
         <v>62</v>
       </c>
       <c r="F139">
-        <v>0.28982625000000001</v>
+        <v>0.22461534375000003</v>
       </c>
       <c r="G139">
         <v>1365</v>
@@ -10485,7 +10485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EBDBA2-A55D-4618-876A-5B5F7FDFFDB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F46FB5-5D2E-4444-A083-C62549828640}">
   <dimension ref="B9:V30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11787,7 +11787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD959E6B-ADB7-47B2-9ECD-CDBE646B4CDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2CE93B-E02F-4A17-8753-858B60D773D9}">
   <dimension ref="B9:V181"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11881,7 +11881,7 @@
         <v>0.03</v>
       </c>
       <c r="H11">
-        <v>0.29760000000000003</v>
+        <v>0.20832000000000001</v>
       </c>
       <c r="I11">
         <v>4252.5</v>
@@ -11940,7 +11940,7 @@
         <v>0.19</v>
       </c>
       <c r="H12">
-        <v>0.30690000000000001</v>
+        <v>0.21483000000000002</v>
       </c>
       <c r="I12">
         <v>3622.4999999999995</v>
@@ -11999,7 +11999,7 @@
         <v>0.6</v>
       </c>
       <c r="H13">
-        <v>0.40455000000000002</v>
+        <v>0.28318500000000002</v>
       </c>
       <c r="I13">
         <v>2160</v>
@@ -12058,7 +12058,7 @@
         <v>0.6</v>
       </c>
       <c r="H14">
-        <v>0.41385000000000005</v>
+        <v>0.28969500000000004</v>
       </c>
       <c r="I14">
         <v>2160</v>
@@ -12117,7 +12117,7 @@
         <v>6.6765601135218886E-2</v>
       </c>
       <c r="H15">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L15">
         <v>33</v>
@@ -12167,7 +12167,7 @@
         <v>0.17331237294683902</v>
       </c>
       <c r="H16">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L16">
         <v>33</v>
@@ -12217,7 +12217,7 @@
         <v>6.9547501182519678E-2</v>
       </c>
       <c r="H17">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L17">
         <v>33</v>
@@ -12267,7 +12267,7 @@
         <v>4.1728500709511805E-2</v>
       </c>
       <c r="H18">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L18">
         <v>33</v>
@@ -12317,7 +12317,7 @@
         <v>0.88200000000000001</v>
       </c>
       <c r="H19">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I19">
         <v>900</v>
@@ -12376,7 +12376,7 @@
         <v>0.86699999999999999</v>
       </c>
       <c r="H20">
-        <v>0.53939999999999999</v>
+        <v>0.41803500000000005</v>
       </c>
       <c r="I20">
         <v>900</v>
@@ -12435,7 +12435,7 @@
         <v>0.432</v>
       </c>
       <c r="H21">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I21">
         <v>900</v>
@@ -12494,7 +12494,7 @@
         <v>0.86699999999999999</v>
       </c>
       <c r="H22">
-        <v>0.53939999999999999</v>
+        <v>0.41803500000000005</v>
       </c>
       <c r="I22">
         <v>900</v>
@@ -12553,7 +12553,7 @@
         <v>2.4</v>
       </c>
       <c r="H23">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="I23">
         <v>900</v>
@@ -12612,7 +12612,7 @@
         <v>1.0269999999999999</v>
       </c>
       <c r="H24">
-        <v>0.48825000000000007</v>
+        <v>0.37839375000000008</v>
       </c>
       <c r="I24">
         <v>900</v>
@@ -12671,7 +12671,7 @@
         <v>0.61599999999999999</v>
       </c>
       <c r="H25">
-        <v>0.41850000000000009</v>
+        <v>0.32433750000000006</v>
       </c>
       <c r="I25">
         <v>900</v>
@@ -12730,7 +12730,7 @@
         <v>0.94799999999999995</v>
       </c>
       <c r="H26">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I26">
         <v>900</v>
@@ -12789,7 +12789,7 @@
         <v>0.96899999999999997</v>
       </c>
       <c r="H27">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I27">
         <v>900</v>
@@ -12848,7 +12848,7 @@
         <v>1.4319999999999999</v>
       </c>
       <c r="H28">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I28">
         <v>900</v>
@@ -12907,7 +12907,7 @@
         <v>0.72829999999999995</v>
       </c>
       <c r="H29">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I29">
         <v>900</v>
@@ -12966,7 +12966,7 @@
         <v>0.72799999999999998</v>
       </c>
       <c r="H30">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I30">
         <v>900</v>
@@ -13025,7 +13025,7 @@
         <v>0.72829999999999995</v>
       </c>
       <c r="H31">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I31">
         <v>900</v>
@@ -13084,7 +13084,7 @@
         <v>0.7</v>
       </c>
       <c r="H32">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I32">
         <v>900</v>
@@ -13143,7 +13143,7 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="H33">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="I33">
         <v>900</v>
@@ -13202,7 +13202,7 @@
         <v>1.337</v>
       </c>
       <c r="H34">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I34">
         <v>900</v>
@@ -13261,7 +13261,7 @@
         <v>0.6</v>
       </c>
       <c r="H35">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="I35">
         <v>900</v>
@@ -13320,7 +13320,7 @@
         <v>0.6</v>
       </c>
       <c r="H36">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="I36">
         <v>900</v>
@@ -13379,7 +13379,7 @@
         <v>0.6</v>
       </c>
       <c r="H37">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="I37">
         <v>900</v>
@@ -13438,7 +13438,7 @@
         <v>1.615</v>
       </c>
       <c r="H38">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I38">
         <v>900</v>
@@ -13497,7 +13497,7 @@
         <v>0.82050000000000001</v>
       </c>
       <c r="H39">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999993</v>
       </c>
       <c r="I39">
         <v>900</v>
@@ -13556,7 +13556,7 @@
         <v>0.82050000000000001</v>
       </c>
       <c r="H40">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999993</v>
       </c>
       <c r="I40">
         <v>900</v>
@@ -13615,7 +13615,7 @@
         <v>0.82350000000000001</v>
       </c>
       <c r="H41">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I41">
         <v>900</v>
@@ -13674,7 +13674,7 @@
         <v>0.82350000000000001</v>
       </c>
       <c r="H42">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I42">
         <v>900</v>
@@ -13733,7 +13733,7 @@
         <v>1.6725000000000001</v>
       </c>
       <c r="H43">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I43">
         <v>900</v>
@@ -13792,7 +13792,7 @@
         <v>0.71</v>
       </c>
       <c r="H44">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I44">
         <v>900</v>
@@ -13851,7 +13851,7 @@
         <v>0.33789999999999998</v>
       </c>
       <c r="H45">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I45">
         <v>900.00000000000011</v>
@@ -13910,7 +13910,7 @@
         <v>1.0409999999999999</v>
       </c>
       <c r="H46">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I46">
         <v>900</v>
@@ -13969,7 +13969,7 @@
         <v>0.64</v>
       </c>
       <c r="H47">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="I47">
         <v>900</v>
@@ -14028,7 +14028,7 @@
         <v>2.35</v>
       </c>
       <c r="H48">
-        <v>0.37200000000000005</v>
+        <v>0.28830000000000006</v>
       </c>
       <c r="I48">
         <v>900</v>
@@ -14087,7 +14087,7 @@
         <v>1.55</v>
       </c>
       <c r="H49">
-        <v>0.53939999999999999</v>
+        <v>0.41803499999999999</v>
       </c>
       <c r="I49">
         <v>900</v>
@@ -14146,7 +14146,7 @@
         <v>0.82499999999999996</v>
       </c>
       <c r="H50">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I50">
         <v>900</v>
@@ -14205,7 +14205,7 @@
         <v>0.82499999999999996</v>
       </c>
       <c r="H51">
-        <v>0.50685000000000002</v>
+        <v>0.39280875000000004</v>
       </c>
       <c r="I51">
         <v>900</v>
@@ -14264,7 +14264,7 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="H52">
-        <v>0.55800000000000005</v>
+        <v>0.43245000000000006</v>
       </c>
       <c r="I52">
         <v>900</v>
@@ -14323,7 +14323,7 @@
         <v>1.706</v>
       </c>
       <c r="H53">
-        <v>0.50685000000000002</v>
+        <v>0.3928087500000001</v>
       </c>
       <c r="I53">
         <v>900</v>
@@ -14382,7 +14382,7 @@
         <v>0.1</v>
       </c>
       <c r="H54">
-        <v>0.21390000000000001</v>
+        <v>0.16577250000000002</v>
       </c>
       <c r="I54">
         <v>827.99999999999989</v>
@@ -14441,7 +14441,7 @@
         <v>0.1</v>
       </c>
       <c r="H55">
-        <v>0.21390000000000001</v>
+        <v>0.16577250000000002</v>
       </c>
       <c r="I55">
         <v>827.99999999999989</v>
@@ -14500,7 +14500,7 @@
         <v>0.1012</v>
       </c>
       <c r="H56">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="I56">
         <v>827.99999999999989</v>
@@ -14559,7 +14559,7 @@
         <v>0.1012</v>
       </c>
       <c r="H57">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="I57">
         <v>827.99999999999989</v>
@@ -14618,7 +14618,7 @@
         <v>0.1012</v>
       </c>
       <c r="H58">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="I58">
         <v>827.99999999999989</v>
@@ -14677,7 +14677,7 @@
         <v>0.1012</v>
       </c>
       <c r="H59">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="I59">
         <v>827.99999999999989</v>
@@ -14736,7 +14736,7 @@
         <v>0.1012</v>
       </c>
       <c r="H60">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="I60">
         <v>827.99999999999989</v>
@@ -14795,7 +14795,7 @@
         <v>0.1012</v>
       </c>
       <c r="H61">
-        <v>0.24645000000000006</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="I61">
         <v>827.99999999999989</v>
@@ -14854,7 +14854,7 @@
         <v>0.14030000000000001</v>
       </c>
       <c r="H62">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I62">
         <v>827.99999999999989</v>
@@ -14913,7 +14913,7 @@
         <v>0.14030000000000001</v>
       </c>
       <c r="H63">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I63">
         <v>827.99999999999989</v>
@@ -14972,7 +14972,7 @@
         <v>0.14030000000000001</v>
       </c>
       <c r="H64">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I64">
         <v>827.99999999999989</v>
@@ -15031,7 +15031,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="H65">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I65">
         <v>827.99999999999989</v>
@@ -15090,7 +15090,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="H66">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I66">
         <v>827.99999999999989</v>
@@ -15149,7 +15149,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="H67">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I67">
         <v>827.99999999999989</v>
@@ -15208,7 +15208,7 @@
         <v>0.24199999999999999</v>
       </c>
       <c r="H68">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I68">
         <v>827.99999999999989</v>
@@ -15267,7 +15267,7 @@
         <v>0.2717</v>
       </c>
       <c r="H69">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="I69">
         <v>827.99999999999989</v>
@@ -15326,7 +15326,7 @@
         <v>0.2717</v>
       </c>
       <c r="H70">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="I70">
         <v>827.99999999999989</v>
@@ -15385,7 +15385,7 @@
         <v>0.2717</v>
       </c>
       <c r="H71">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="I71">
         <v>827.99999999999989</v>
@@ -15444,7 +15444,7 @@
         <v>0.126</v>
       </c>
       <c r="H72">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I72">
         <v>827.99999999999989</v>
@@ -15503,7 +15503,7 @@
         <v>0.126</v>
       </c>
       <c r="H73">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I73">
         <v>827.99999999999989</v>
@@ -15562,7 +15562,7 @@
         <v>0.81799999999999995</v>
       </c>
       <c r="H74">
-        <v>0.25575000000000003</v>
+        <v>0.19820625000000003</v>
       </c>
       <c r="I74">
         <v>720</v>
@@ -15621,7 +15621,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H75">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="I75">
         <v>827.99999999999989</v>
@@ -15680,7 +15680,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="H76">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000004</v>
       </c>
       <c r="I76">
         <v>827.99999999999989</v>
@@ -15739,7 +15739,7 @@
         <v>0.123</v>
       </c>
       <c r="H77">
-        <v>0.24645000000000003</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="I77">
         <v>827.99999999999989</v>
@@ -15798,7 +15798,7 @@
         <v>0.123</v>
       </c>
       <c r="H78">
-        <v>0.24645000000000003</v>
+        <v>0.19099875000000002</v>
       </c>
       <c r="I78">
         <v>827.99999999999989</v>
@@ -15857,7 +15857,7 @@
         <v>0.09</v>
       </c>
       <c r="H79">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="I79">
         <v>827.99999999999989</v>
@@ -15916,7 +15916,7 @@
         <v>0.09</v>
       </c>
       <c r="H80">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="I80">
         <v>827.99999999999989</v>
@@ -15975,7 +15975,7 @@
         <v>0.09</v>
       </c>
       <c r="H81">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="I81">
         <v>827.99999999999989</v>
@@ -16034,7 +16034,7 @@
         <v>0.09</v>
       </c>
       <c r="H82">
-        <v>0.2883</v>
+        <v>0.22343249999999998</v>
       </c>
       <c r="I82">
         <v>827.99999999999989</v>
@@ -16093,7 +16093,7 @@
         <v>0.16250000000000001</v>
       </c>
       <c r="H83">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="I83">
         <v>827.99999999999977</v>
@@ -16152,7 +16152,7 @@
         <v>0.16250000000000001</v>
       </c>
       <c r="H84">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="I84">
         <v>827.99999999999977</v>
@@ -16211,7 +16211,7 @@
         <v>0.1</v>
       </c>
       <c r="H85">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="I85">
         <v>827.99999999999989</v>
@@ -16270,7 +16270,7 @@
         <v>0.1</v>
       </c>
       <c r="H86">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I86">
         <v>827.99999999999989</v>
@@ -16329,7 +16329,7 @@
         <v>0.1</v>
       </c>
       <c r="H87">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I87">
         <v>827.99999999999989</v>
@@ -16388,7 +16388,7 @@
         <v>0.1</v>
       </c>
       <c r="H88">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I88">
         <v>827.99999999999989</v>
@@ -16447,7 +16447,7 @@
         <v>0.1</v>
       </c>
       <c r="H89">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I89">
         <v>827.99999999999989</v>
@@ -16506,7 +16506,7 @@
         <v>0.08</v>
       </c>
       <c r="H90">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I90">
         <v>827.99999999999977</v>
@@ -16565,7 +16565,7 @@
         <v>0.08</v>
       </c>
       <c r="H91">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I91">
         <v>827.99999999999977</v>
@@ -16624,7 +16624,7 @@
         <v>0.05</v>
       </c>
       <c r="H92">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="I92">
         <v>972</v>
@@ -16683,7 +16683,7 @@
         <v>0.05</v>
       </c>
       <c r="H93">
-        <v>0.26040000000000002</v>
+        <v>0.20181000000000002</v>
       </c>
       <c r="I93">
         <v>972</v>
@@ -16742,7 +16742,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="H94">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="I94">
         <v>827.99999999999989</v>
@@ -16801,7 +16801,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="H95">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="I95">
         <v>827.99999999999989</v>
@@ -16860,7 +16860,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="H96">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="I96">
         <v>827.99999999999989</v>
@@ -16919,7 +16919,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="H97">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="I97">
         <v>827.99999999999989</v>
@@ -16978,7 +16978,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="H98">
-        <v>0.2883</v>
+        <v>0.22343250000000001</v>
       </c>
       <c r="I98">
         <v>827.99999999999989</v>
@@ -17037,7 +17037,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="H99">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I99">
         <v>827.99999999999989</v>
@@ -17096,7 +17096,7 @@
         <v>0.26500000000000001</v>
       </c>
       <c r="H100">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I100">
         <v>827.99999999999989</v>
@@ -17155,7 +17155,7 @@
         <v>0.16250000000000001</v>
       </c>
       <c r="H101">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="I101">
         <v>827.99999999999977</v>
@@ -17214,7 +17214,7 @@
         <v>0.16250000000000001</v>
       </c>
       <c r="H102">
-        <v>0.2697</v>
+        <v>0.20901750000000002</v>
       </c>
       <c r="I102">
         <v>827.99999999999977</v>
@@ -17273,7 +17273,7 @@
         <v>0.187</v>
       </c>
       <c r="H103">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I103">
         <v>827.99999999999989</v>
@@ -17332,7 +17332,7 @@
         <v>0.1</v>
       </c>
       <c r="H104">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I104">
         <v>827.99999999999989</v>
@@ -17391,7 +17391,7 @@
         <v>0.1</v>
       </c>
       <c r="H105">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I105">
         <v>827.99999999999989</v>
@@ -17450,7 +17450,7 @@
         <v>0.1</v>
       </c>
       <c r="H106">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="I106">
         <v>827.99999999999989</v>
@@ -17509,7 +17509,7 @@
         <v>0.1</v>
       </c>
       <c r="H107">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="I107">
         <v>827.99999999999989</v>
@@ -17568,7 +17568,7 @@
         <v>0.1</v>
       </c>
       <c r="H108">
-        <v>0.24645000000000003</v>
+        <v>0.19099874999999999</v>
       </c>
       <c r="I108">
         <v>827.99999999999989</v>
@@ -17627,7 +17627,7 @@
         <v>0.126</v>
       </c>
       <c r="H109">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I109">
         <v>827.99999999999989</v>
@@ -17686,7 +17686,7 @@
         <v>0.126</v>
       </c>
       <c r="H110">
-        <v>0.2697</v>
+        <v>0.20901749999999999</v>
       </c>
       <c r="I110">
         <v>827.99999999999989</v>
@@ -17745,7 +17745,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="H111">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="I111">
         <v>1242</v>
@@ -17804,7 +17804,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="H112">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="I112">
         <v>1242</v>
@@ -17863,7 +17863,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="H113">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="I113">
         <v>1242</v>
@@ -17922,7 +17922,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="H114">
-        <v>0.29760000000000003</v>
+        <v>0.23064000000000001</v>
       </c>
       <c r="I114">
         <v>1242</v>
@@ -17981,7 +17981,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="H115">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="I115">
         <v>1242</v>
@@ -18040,7 +18040,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="H116">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="I116">
         <v>1242</v>
@@ -18099,7 +18099,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="H117">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="I117">
         <v>1242</v>
@@ -18158,7 +18158,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="H118">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="I118">
         <v>1242</v>
@@ -18217,7 +18217,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="H119">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="I119">
         <v>1242</v>
@@ -18276,7 +18276,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="H120">
-        <v>0.30690000000000001</v>
+        <v>0.23784749999999999</v>
       </c>
       <c r="I120">
         <v>1242</v>
@@ -18335,7 +18335,7 @@
         <v>0.23</v>
       </c>
       <c r="H121">
-        <v>0.32084999999999997</v>
+        <v>0.24865874999999998</v>
       </c>
       <c r="I121">
         <v>1242</v>
@@ -18394,7 +18394,7 @@
         <v>0.33600000000000002</v>
       </c>
       <c r="H122">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="I122">
         <v>1080</v>
@@ -18453,7 +18453,7 @@
         <v>0.06</v>
       </c>
       <c r="H123">
-        <v>0.32084999999999997</v>
+        <v>0.24865874999999998</v>
       </c>
       <c r="I123">
         <v>1242</v>
@@ -18512,7 +18512,7 @@
         <v>0.6</v>
       </c>
       <c r="H124">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="I124">
         <v>1080</v>
@@ -18571,7 +18571,7 @@
         <v>0.6</v>
       </c>
       <c r="H125">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="I125">
         <v>1080</v>
@@ -18630,7 +18630,7 @@
         <v>0.6</v>
       </c>
       <c r="H126">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="I126">
         <v>1080</v>
@@ -18689,7 +18689,7 @@
         <v>0.6</v>
       </c>
       <c r="H127">
-        <v>0.33945000000000003</v>
+        <v>0.26307375000000005</v>
       </c>
       <c r="I127">
         <v>1080</v>
@@ -18748,7 +18748,7 @@
         <v>6.9547501182519678E-2</v>
       </c>
       <c r="H128">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L128">
         <v>33</v>
@@ -18798,7 +18798,7 @@
         <v>3.3660990572339525E-2</v>
       </c>
       <c r="H129">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L129">
         <v>33</v>
@@ -18848,7 +18848,7 @@
         <v>4.3731468743568369E-2</v>
       </c>
       <c r="H130">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L130">
         <v>33</v>
@@ -18898,7 +18898,7 @@
         <v>7.8204774129719712E-2</v>
       </c>
       <c r="H131">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L131">
         <v>33</v>
@@ -18948,7 +18948,7 @@
         <v>0.25801010178695877</v>
       </c>
       <c r="H132">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L132">
         <v>33</v>
@@ -18998,7 +18998,7 @@
         <v>0.13639655931915756</v>
       </c>
       <c r="H133">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L133">
         <v>33</v>
@@ -19048,7 +19048,7 @@
         <v>0.15155791457694689</v>
       </c>
       <c r="H134">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L134">
         <v>33</v>
@@ -19098,7 +19098,7 @@
         <v>2.9488140501388344E-2</v>
       </c>
       <c r="H135">
-        <v>0.33123000000000008</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L135">
         <v>33</v>
@@ -19148,7 +19148,7 @@
         <v>6.9658777184411699E-2</v>
       </c>
       <c r="H136">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L136">
         <v>33</v>
@@ -19198,7 +19198,7 @@
         <v>4.7208843802694356E-2</v>
       </c>
       <c r="H137">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L137">
         <v>33</v>
@@ -19248,7 +19248,7 @@
         <v>8.3178811414293535E-2</v>
       </c>
       <c r="H138">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L138">
         <v>33</v>
@@ -19298,7 +19298,7 @@
         <v>1.2435093211434519E-2</v>
       </c>
       <c r="H139">
-        <v>0.33123000000000008</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L139">
         <v>33</v>
@@ -19348,7 +19348,7 @@
         <v>4.7459214806951429E-2</v>
       </c>
       <c r="H140">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L140">
         <v>33</v>
@@ -19398,7 +19398,7 @@
         <v>0.12900783279352668</v>
       </c>
       <c r="H141">
-        <v>0.33123000000000002</v>
+        <v>0.25670325000000005</v>
       </c>
       <c r="L141">
         <v>33</v>
@@ -21608,7 +21608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64994F28-E2C1-4FC4-A78E-C4C394C4B085}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99097BE9-55D6-4F8A-AF6C-3B2C73A3C1B1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ARE_grids_kan/vt_vervestacks_ARE_v1.xlsx
+++ b/VerveStacks_ARE_grids_kan/vt_vervestacks_ARE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29A0C185-B261-4B45-A9F8-9E8D961B3A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18DD3D8A-C96A-4B45-A7AD-9C85CAD13E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CC49AEDB-DEEA-48B4-8487-5425ADBB12A0}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BE202756-A5F7-447B-A2E1-C0324CFA8AF4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2407,7 +2407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53C7464-69EB-4D21-B03B-96C5A022AE94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07827A87-68E3-4EBF-980F-1DCCDA1852F2}">
   <dimension ref="B9:V139"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10485,7 +10485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F46FB5-5D2E-4444-A083-C62549828640}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BE9A5B-F3F3-47F1-9890-7D6002B39C73}">
   <dimension ref="B9:V30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11787,7 +11787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2CE93B-E02F-4A17-8753-858B60D773D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2CCDE8-B768-4A34-9875-B10DACC7AD68}">
   <dimension ref="B9:V181"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19894,7 +19894,7 @@
         <v>14</v>
       </c>
       <c r="R149" t="s">
-        <v>218</v>
+        <v>353</v>
       </c>
       <c r="S149" t="s">
         <v>219</v>
@@ -19956,7 +19956,7 @@
         <v>14</v>
       </c>
       <c r="R150" t="s">
-        <v>353</v>
+        <v>218</v>
       </c>
       <c r="S150" t="s">
         <v>219</v>
@@ -21608,7 +21608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99097BE9-55D6-4F8A-AF6C-3B2C73A3C1B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4459723B-4EE5-411E-A643-057514C81499}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_ARE_grids_kan/vt_vervestacks_ARE_v1.xlsx
+++ b/VerveStacks_ARE_grids_kan/vt_vervestacks_ARE_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ARE_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18DD3D8A-C96A-4B45-A7AD-9C85CAD13E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C20CBA5-6098-45C7-A599-AC73C270D7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{BE202756-A5F7-447B-A2E1-C0324CFA8AF4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A9E76096-7FB2-46BF-BDB8-FFC818A170EA}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2407,7 +2407,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07827A87-68E3-4EBF-980F-1DCCDA1852F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A183E9C-2168-4846-B81B-19AA07EC02C8}">
   <dimension ref="B9:V139"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10485,7 +10485,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BE9A5B-F3F3-47F1-9890-7D6002B39C73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2CF63B8-DA8A-4E60-89B5-0F9D9BD25405}">
   <dimension ref="B9:V30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11787,7 +11787,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2CCDE8-B768-4A34-9875-B10DACC7AD68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8679DABA-B041-4C3D-8478-7D6487295D5A}">
   <dimension ref="B9:V181"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21608,7 +21608,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4459723B-4EE5-411E-A643-057514C81499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEAA3F09-96D4-4519-8184-242269A321C1}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
